--- a/awatifNarratif/ig/CdaToPractitionerConceptMap.xlsx
+++ b/awatifNarratif/ig/CdaToPractitionerConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:08:47+00:00</t>
+    <t>2026-03-17T13:21:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/awatifNarratif/ig/CdaToPractitionerConceptMap.xlsx
+++ b/awatifNarratif/ig/CdaToPractitionerConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:21:46+00:00</t>
+    <t>2026-03-17T16:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
